--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486802_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486802_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>7.321</v>
+        <v>8.8559</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2398</v>
+        <v>5.3774</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0812</v>
+        <v>3.4785</v>
       </c>
       <c r="G2" t="n">
         <v>3.6588</v>
@@ -610,13 +610,13 @@
         <v>3.0892</v>
       </c>
       <c r="S2" t="n">
-        <v>-1.8591</v>
+        <v>-0.3242</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.883</v>
+        <v>0.2546</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.9761</v>
+        <v>-0.5788</v>
       </c>
       <c r="V2" t="n">
         <v>3.3975</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.744</v>
+        <v>2.7358</v>
       </c>
       <c r="E3" t="n">
-        <v>0.7397</v>
+        <v>0.5329</v>
       </c>
       <c r="F3" t="n">
-        <v>2.0042</v>
+        <v>2.2029</v>
       </c>
       <c r="G3" t="n">
         <v>1.4078</v>
@@ -688,13 +688,13 @@
         <v>2.8962</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.309</v>
+        <v>-0.3172</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6615</v>
+        <v>0.4546</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.9705</v>
+        <v>-0.7718</v>
       </c>
       <c r="V3" t="n">
         <v>-0.2856</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. THIAW</t>
+          <t>D. DAMIAN</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.73</v>
+        <v>1.9312</v>
       </c>
       <c r="E4" t="n">
-        <v>0.88</v>
+        <v>-1.0468</v>
       </c>
       <c r="F4" t="n">
-        <v>1.85</v>
+        <v>2.978</v>
       </c>
       <c r="G4" t="n">
-        <v>3.81</v>
+        <v>3.2276</v>
       </c>
       <c r="H4" t="n">
-        <v>3.7241</v>
+        <v>2.2894</v>
       </c>
       <c r="I4" t="n">
-        <v>0.0859</v>
+        <v>0.9382</v>
       </c>
       <c r="J4" t="n">
-        <v>3.8593</v>
+        <v>2.5807</v>
       </c>
       <c r="K4" t="n">
-        <v>3.6559</v>
+        <v>1.3938</v>
       </c>
       <c r="L4" t="n">
-        <v>0.2035</v>
+        <v>1.1869</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.0494</v>
+        <v>0.6469</v>
       </c>
       <c r="N4" t="n">
-        <v>0.0682</v>
+        <v>0.8956</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1176</v>
+        <v>-0.2487</v>
       </c>
       <c r="P4" t="n">
-        <v>-1.1585</v>
+        <v>-1.3515</v>
       </c>
       <c r="Q4" t="n">
         <v>-3.8616</v>
       </c>
       <c r="R4" t="n">
-        <v>2.7031</v>
+        <v>2.51</v>
       </c>
       <c r="S4" t="n">
-        <v>1.92</v>
+        <v>0.0552</v>
       </c>
       <c r="T4" t="n">
-        <v>0.8822</v>
+        <v>0.234</v>
       </c>
       <c r="U4" t="n">
-        <v>1.0378</v>
+        <v>-0.1789</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.8415</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.8415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MEJIA ECHEVERRY</t>
+          <t>M. THIAW</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6453</v>
+        <v>1.9065</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4816</v>
+        <v>0.7766</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1268</v>
+        <v>1.1299</v>
       </c>
       <c r="G5" t="n">
-        <v>0.3585</v>
+        <v>3.81</v>
       </c>
       <c r="H5" t="n">
-        <v>0.6276</v>
+        <v>3.7241</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.269</v>
+        <v>0.0859</v>
       </c>
       <c r="J5" t="n">
-        <v>0.7326</v>
+        <v>3.8593</v>
       </c>
       <c r="K5" t="n">
-        <v>0.0769</v>
+        <v>3.6559</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6556999999999999</v>
+        <v>0.2035</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.374</v>
+        <v>-0.0494</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5506</v>
+        <v>0.0682</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.9247</v>
+        <v>-0.1176</v>
       </c>
       <c r="P5" t="n">
-        <v>2.3169</v>
+        <v>-1.1585</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9654</v>
+        <v>-3.8616</v>
       </c>
       <c r="R5" t="n">
-        <v>3.2823</v>
+        <v>2.7031</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7446</v>
+        <v>1.0965</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.2487</v>
+        <v>0.7788</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.4959</v>
+        <v>0.3177</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.2856</v>
+        <v>-1.8415</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2856</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>D. DAMIAN</t>
+          <t>J. MEJIA ECHEVERRY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5009</v>
+        <v>1.8314</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2537</v>
+        <v>-0.1713</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7546</v>
+        <v>2.0027</v>
       </c>
       <c r="G6" t="n">
-        <v>3.2276</v>
+        <v>0.3585</v>
       </c>
       <c r="H6" t="n">
-        <v>2.2894</v>
+        <v>0.6276</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9382</v>
+        <v>-0.269</v>
       </c>
       <c r="J6" t="n">
-        <v>2.5807</v>
+        <v>0.7326</v>
       </c>
       <c r="K6" t="n">
-        <v>1.3938</v>
+        <v>0.0769</v>
       </c>
       <c r="L6" t="n">
-        <v>1.1869</v>
+        <v>0.6556999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>0.6469</v>
+        <v>-0.374</v>
       </c>
       <c r="N6" t="n">
-        <v>0.8956</v>
+        <v>0.5506</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.2487</v>
+        <v>-0.9247</v>
       </c>
       <c r="P6" t="n">
-        <v>-1.3515</v>
+        <v>2.3169</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R6" t="n">
-        <v>2.51</v>
+        <v>3.2823</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3752</v>
+        <v>-0.5585</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0272</v>
+        <v>0.0615</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4024</v>
+        <v>-0.62</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. CAULIN TORNERO</t>
+          <t>M. MELERO JAREÑO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.988</v>
+        <v>1.6596</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0553</v>
+        <v>2.3627</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.0673</v>
+        <v>-0.703</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.2001</v>
+        <v>0.2031</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2965</v>
+        <v>1.2272</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.4966</v>
+        <v>-1.0241</v>
       </c>
       <c r="J7" t="n">
-        <v>0.4562</v>
+        <v>1.204</v>
       </c>
       <c r="K7" t="n">
-        <v>1.0213</v>
+        <v>1.1588</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.5651</v>
+        <v>0.0453</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.6563</v>
+        <v>-1.0009</v>
       </c>
       <c r="N7" t="n">
-        <v>0.2752</v>
+        <v>0.0684</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9314</v>
+        <v>-1.0693</v>
       </c>
       <c r="P7" t="n">
-        <v>1.1585</v>
+        <v>0.7723</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9654</v>
       </c>
       <c r="R7" t="n">
-        <v>2.1239</v>
+        <v>1.7377</v>
       </c>
       <c r="S7" t="n">
-        <v>2.1567</v>
+        <v>-0.5861</v>
       </c>
       <c r="T7" t="n">
-        <v>2.5645</v>
+        <v>0.2825</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4078</v>
+        <v>-0.8686</v>
       </c>
       <c r="V7" t="n">
-        <v>-2.1271</v>
+        <v>1.2703</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="X7" t="n">
-        <v>-2.1271</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MELERO JAREÑO</t>
+          <t>I. KANE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7122000000000001</v>
+        <v>-0.5124</v>
       </c>
       <c r="E8" t="n">
-        <v>1.6387</v>
+        <v>-0.8982</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.9265</v>
+        <v>0.3858</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2031</v>
+        <v>-0.7745</v>
       </c>
       <c r="H8" t="n">
-        <v>1.2272</v>
+        <v>-0.4965</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.0241</v>
+        <v>-0.2781</v>
       </c>
       <c r="J8" t="n">
-        <v>1.204</v>
+        <v>-0.512</v>
       </c>
       <c r="K8" t="n">
-        <v>1.1588</v>
+        <v>-0.634</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0453</v>
+        <v>0.1221</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.0009</v>
+        <v>-0.2626</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0684</v>
+        <v>0.1376</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.0693</v>
+        <v>-0.4002</v>
       </c>
       <c r="P8" t="n">
         <v>0.7723</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>1.7377</v>
+        <v>0.7723</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.5335</v>
+        <v>-0.5102</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4415</v>
+        <v>-0.3863</v>
       </c>
       <c r="U8" t="n">
-        <v>-1.0921</v>
+        <v>-0.1239</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2703</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.8415</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-0.5712</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>I. KANE</t>
+          <t>A. CAULIN TORNERO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.4379</v>
+        <v>-1.0723</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.8982</v>
+        <v>0.1937</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4603</v>
+        <v>-1.266</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.7745</v>
+        <v>-0.2001</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.4965</v>
+        <v>1.2965</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2781</v>
+        <v>-1.4966</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.512</v>
+        <v>0.4562</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.634</v>
+        <v>1.0213</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1221</v>
+        <v>-0.5651</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.2626</v>
+        <v>-0.6563</v>
       </c>
       <c r="N9" t="n">
-        <v>0.1376</v>
+        <v>0.2752</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.4002</v>
+        <v>-0.9314</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7723</v>
+        <v>1.1585</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R9" t="n">
-        <v>0.7723</v>
+        <v>2.1239</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4357</v>
+        <v>0.0965</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3863</v>
+        <v>0.7029</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.0494</v>
+        <v>-0.6064000000000001</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-2.1271</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-2.1271</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.2188</v>
+        <v>-4.3511</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.0002</v>
+        <v>-2.207</v>
       </c>
       <c r="F10" t="n">
-        <v>-2.2186</v>
+        <v>-2.1441</v>
       </c>
       <c r="G10" t="n">
         <v>-3.7933</v>
@@ -1234,13 +1234,13 @@
         <v>1.1585</v>
       </c>
       <c r="S10" t="n">
-        <v>0.215</v>
+        <v>0.08260000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>0.3032</v>
+        <v>0.0964</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.0882</v>
+        <v>-0.0137</v>
       </c>
       <c r="V10" t="n">
         <v>-1.7989</v>
@@ -1267,10 +1267,10 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>12.9847</v>
+        <v>12.9846</v>
       </c>
       <c r="E11" t="n">
-        <v>4.9198</v>
+        <v>4.919999999999999</v>
       </c>
       <c r="F11" t="n">
         <v>8.0647</v>
@@ -1288,7 +1288,7 @@
         <v>10.0801</v>
       </c>
       <c r="K11" t="n">
-        <v>8.9719</v>
+        <v>8.971900000000002</v>
       </c>
       <c r="L11" t="n">
         <v>1.1084</v>
@@ -1303,7 +1303,7 @@
         <v>-4.5895</v>
       </c>
       <c r="P11" t="n">
-        <v>7.723200000000001</v>
+        <v>7.7232</v>
       </c>
       <c r="Q11" t="n">
         <v>-12.5502</v>
@@ -1312,13 +1312,13 @@
         <v>20.2732</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9654000000000004</v>
+        <v>-0.9654</v>
       </c>
       <c r="T11" t="n">
-        <v>2.4791</v>
+        <v>2.479</v>
       </c>
       <c r="U11" t="n">
-        <v>-3.4446</v>
+        <v>-3.4444</v>
       </c>
       <c r="V11" t="n">
         <v>-1.6709</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>2.4021</v>
+        <v>1.8864</v>
       </c>
       <c r="E12" t="n">
-        <v>3.4597</v>
+        <v>2.6323</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.0576</v>
+        <v>-0.7459</v>
       </c>
       <c r="G12" t="n">
         <v>0.8176</v>
@@ -1390,13 +1390,13 @@
         <v>1.5446</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3914</v>
+        <v>-0.1242</v>
       </c>
       <c r="T12" t="n">
-        <v>1.2407</v>
+        <v>0.4133</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.8493000000000001</v>
+        <v>-0.5376</v>
       </c>
       <c r="V12" t="n">
         <v>0.6138</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>2.2395</v>
+        <v>1.4711</v>
       </c>
       <c r="E13" t="n">
-        <v>1.3206</v>
+        <v>1.0104</v>
       </c>
       <c r="F13" t="n">
-        <v>0.9189000000000001</v>
+        <v>0.4608</v>
       </c>
       <c r="G13" t="n">
         <v>0.6556999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>1.3515</v>
       </c>
       <c r="S13" t="n">
-        <v>1.92</v>
+        <v>1.1516</v>
       </c>
       <c r="T13" t="n">
-        <v>1.2131</v>
+        <v>0.9028</v>
       </c>
       <c r="U13" t="n">
-        <v>0.7069</v>
+        <v>0.2489</v>
       </c>
       <c r="V13" t="n">
         <v>0.243</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4559</v>
+        <v>1.0256</v>
       </c>
       <c r="E14" t="n">
-        <v>1.2066</v>
+        <v>1.1032</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.7506</v>
+        <v>-0.0775</v>
       </c>
       <c r="G14" t="n">
         <v>1.398</v>
@@ -1546,13 +1546,13 @@
         <v>2.3169</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0113</v>
+        <v>0.5584</v>
       </c>
       <c r="T14" t="n">
-        <v>1.1027</v>
+        <v>0.9993</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.114</v>
+        <v>-0.4409</v>
       </c>
       <c r="V14" t="n">
         <v>0.6138</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>-0.6189</v>
+        <v>0.5132</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1956</v>
+        <v>0.7352</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.4233</v>
+        <v>-0.222</v>
       </c>
       <c r="G15" t="n">
         <v>0.4927</v>
@@ -1624,13 +1624,13 @@
         <v>1.9308</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8493000000000001</v>
+        <v>0.2828</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.5243</v>
+        <v>0.4065</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.325</v>
+        <v>-0.1237</v>
       </c>
       <c r="V15" t="n">
         <v>-1.2277</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. SANTOLARIA MARTIN</t>
+          <t>G. CAMPOS MARCOS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.9711</v>
+        <v>-1.7802</v>
       </c>
       <c r="E16" t="n">
-        <v>-3.0367</v>
+        <v>-2.3518</v>
       </c>
       <c r="F16" t="n">
-        <v>1.0656</v>
+        <v>0.5715</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.8929</v>
+        <v>-1.41</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.4761</v>
+        <v>-1.7107</v>
       </c>
       <c r="I16" t="n">
-        <v>0.5832000000000001</v>
+        <v>0.3007</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.4853</v>
+        <v>-0.6021</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.6481</v>
+        <v>-0.6067</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1628</v>
+        <v>0.0046</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.4075</v>
+        <v>-0.8079</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.828</v>
+        <v>-1.1039</v>
       </c>
       <c r="O16" t="n">
-        <v>0.4205</v>
+        <v>0.2961</v>
       </c>
       <c r="P16" t="n">
-        <v>-3.6685</v>
+        <v>-2.3169</v>
       </c>
       <c r="Q16" t="n">
-        <v>-4.827</v>
+        <v>-3.8616</v>
       </c>
       <c r="R16" t="n">
-        <v>1.1585</v>
+        <v>1.5446</v>
       </c>
       <c r="S16" t="n">
-        <v>1.3626</v>
+        <v>-0.1378</v>
       </c>
       <c r="T16" t="n">
-        <v>1.0479</v>
+        <v>0.0274</v>
       </c>
       <c r="U16" t="n">
-        <v>0.3147</v>
+        <v>-0.1652</v>
       </c>
       <c r="V16" t="n">
-        <v>1.2277</v>
+        <v>2.0845</v>
       </c>
       <c r="W16" t="n">
-        <v>1.2277</v>
+        <v>2.0845</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>R. TERRATS MADRID</t>
+          <t>N. MARTINEZ DE SAN VICENTE MARTIN</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.1795</v>
+        <v>-2.4555</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.4656</v>
+        <v>-0.9516</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.7139</v>
+        <v>-1.5038</v>
       </c>
       <c r="G17" t="n">
-        <v>-2.752</v>
+        <v>-1.752</v>
       </c>
       <c r="H17" t="n">
-        <v>-1.4475</v>
+        <v>-1.2207</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.3044</v>
+        <v>-0.5313</v>
       </c>
       <c r="J17" t="n">
-        <v>-1.4749</v>
+        <v>-0.6688</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.8260999999999999</v>
+        <v>-0.6688</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6488</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.277</v>
+        <v>-1.0832</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6214</v>
+        <v>-0.5518999999999999</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6556999999999999</v>
+        <v>-0.5313</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.5792</v>
+        <v>0.1931</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3862</v>
+        <v>0.1931</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8661</v>
+        <v>-0.2827</v>
       </c>
       <c r="T17" t="n">
-        <v>0.6891</v>
+        <v>-0.2829</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1769</v>
+        <v>0.0001</v>
       </c>
       <c r="V17" t="n">
-        <v>0.2856</v>
+        <v>-0.6138</v>
       </c>
       <c r="W17" t="n">
-        <v>0.2856</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.6138</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. MARTINEZ DE SAN VICENTE MARTIN</t>
+          <t>J. SANTOLARIA MARTIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-2.5589</v>
+        <v>-2.6027</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.0551</v>
+        <v>-3.6573</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.5038</v>
+        <v>1.0545</v>
       </c>
       <c r="G18" t="n">
-        <v>-1.752</v>
+        <v>-0.8929</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.2207</v>
+        <v>-1.4761</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.5313</v>
+        <v>0.5832000000000001</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.6688</v>
+        <v>-0.4853</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6688</v>
+        <v>-0.6481</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.1628</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.0832</v>
+        <v>-0.4075</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.5518999999999999</v>
+        <v>-0.828</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5313</v>
+        <v>0.4205</v>
       </c>
       <c r="P18" t="n">
-        <v>0.1931</v>
+        <v>-3.6685</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-4.827</v>
       </c>
       <c r="R18" t="n">
-        <v>0.1931</v>
+        <v>1.1585</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.3862</v>
+        <v>0.731</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.3863</v>
+        <v>0.4273</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0001</v>
+        <v>0.3036</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.6138</v>
+        <v>1.2277</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>1.2277</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.6138</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>G. CAMPOS MARCOS</t>
+          <t>R. TERRATS MADRID</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.6187</v>
+        <v>-2.6388</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.7654</v>
+        <v>-1.7758</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1467</v>
+        <v>-0.8629</v>
       </c>
       <c r="G19" t="n">
-        <v>-1.41</v>
+        <v>-2.752</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.7107</v>
+        <v>-1.4475</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3007</v>
+        <v>-1.3044</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6021</v>
+        <v>-1.4749</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.6067</v>
+        <v>-0.8260999999999999</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0046</v>
+        <v>-0.6488</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.8079</v>
+        <v>-1.277</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1039</v>
+        <v>-0.6214</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2961</v>
+        <v>-0.6556999999999999</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.3169</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.8616</v>
+        <v>-0.9654</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5446</v>
+        <v>0.3862</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9762999999999999</v>
+        <v>0.4068</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.3863</v>
+        <v>0.3789</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.59</v>
+        <v>0.0279</v>
       </c>
       <c r="V19" t="n">
-        <v>2.0845</v>
+        <v>0.2856</v>
       </c>
       <c r="W19" t="n">
-        <v>2.0845</v>
+        <v>0.2856</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.9435</v>
+        <v>-3.1158</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.7222</v>
+        <v>-2.0324</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2213</v>
+        <v>-1.0834</v>
       </c>
       <c r="G20" t="n">
         <v>-2.222</v>
@@ -2014,13 +2014,13 @@
         <v>1.1585</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0275</v>
+        <v>-0.1448</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3032</v>
+        <v>-0.0071</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2757</v>
+        <v>-0.1378</v>
       </c>
       <c r="V20" t="n">
         <v>-0.9421</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-5.1915</v>
+        <v>-3.909</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.8111</v>
+        <v>-2.7768</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.3804</v>
+        <v>-1.1321</v>
       </c>
       <c r="G21" t="n">
         <v>-2.2331</v>
@@ -2092,13 +2092,13 @@
         <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.3792</v>
+        <v>-0.09669999999999999</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.8554</v>
+        <v>0.1788</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.5238</v>
+        <v>-0.2755</v>
       </c>
       <c r="V21" t="n">
         <v>-0.6138</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-12.9846</v>
+        <v>-11.6057</v>
       </c>
       <c r="E22" t="n">
-        <v>-8.0648</v>
+        <v>-8.0646</v>
       </c>
       <c r="F22" t="n">
-        <v>-4.9197</v>
+        <v>-3.5408</v>
       </c>
       <c r="G22" t="n">
         <v>-7.898</v>
@@ -2170,13 +2170,13 @@
         <v>12.5501</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9653</v>
+        <v>2.3444</v>
       </c>
       <c r="T22" t="n">
-        <v>3.444400000000001</v>
+        <v>3.4443</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.479200000000001</v>
+        <v>-1.1002</v>
       </c>
       <c r="V22" t="n">
         <v>1.671</v>
